--- a/wealthscale/WealthScale_201_Pages_Index.xlsx
+++ b/wealthscale/WealthScale_201_Pages_Index.xlsx
@@ -15885,7 +15885,7 @@
       </c>
       <c r="M101" s="10" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done Oct 27 (published before written legal approval; draft note removed)</t>
         </is>
       </c>
     </row>
@@ -15948,7 +15948,7 @@
       </c>
       <c r="M102" s="10" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done Oct 27 (published before written legal approval; draft note removed)</t>
         </is>
       </c>
     </row>
@@ -16007,7 +16007,7 @@
           <t>Why</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -16037,7 +16037,7 @@
           <t>The old page is no longer part of the site plan; this page takes its place</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>Done Oct 27: published, 301 added, old page in Trash</t>
         </is>
@@ -16067,7 +16067,7 @@
           <t>The old page is no longer part of the site plan; this page takes its place</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>Done Oct 27: published, 301 added, old page in Trash</t>
         </is>
@@ -16097,7 +16097,7 @@
           <t>The old page is no longer part of the site plan; this page takes its place</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>Done Oct 27: published, 301 added, old page in Trash</t>
         </is>

--- a/wealthscale/WealthScale_201_Pages_Index.xlsx
+++ b/wealthscale/WealthScale_201_Pages_Index.xlsx
@@ -12060,11 +12060,11 @@
       </c>
       <c r="E3" s="3" t="n">
         <f aca="false">COUNTIFS('First 101 pages (latest)'!A$2:A$102,B3,'First 101 pages (latest)'!M$2:M$102,"Done")</f>
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="F3" s="3" t="n">
         <f aca="false">D3-E3</f>
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="G3" s="5" t="n">
         <f aca="false">SUMIF('First 101 pages (latest)'!A$2:A$102,B3,'First 101 pages (latest)'!L$2:L$102)</f>
@@ -12241,11 +12241,11 @@
       </c>
       <c r="E10" s="3" t="n">
         <f aca="false">SUM(E2:E9)</f>
-        <v>52</v>
+        <v>101</v>
       </c>
       <c r="F10" s="3" t="n">
         <f aca="false">SUM(F2:F9)</f>
-        <v>149</v>
+        <v>100</v>
       </c>
       <c r="G10" s="5" t="n">
         <f aca="false">SUM(G2:G9)</f>
@@ -14415,7 +14415,7 @@
         <v>7303</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14456,7 +14456,7 @@
         <v>7316</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14497,7 +14497,7 @@
         <v>13645</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14538,7 +14538,7 @@
         <v>9472</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14579,7 +14579,7 @@
         <v>11122</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14620,7 +14620,7 @@
         <v>11797</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14661,7 +14661,7 @@
         <v>11185</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14702,7 +14702,7 @@
         <v>9526</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14743,7 +14743,7 @@
         <v>10260</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14784,7 +14784,7 @@
         <v>11548</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14825,7 +14825,7 @@
         <v>9775</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14866,7 +14866,7 @@
         <v>10327</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14907,7 +14907,7 @@
         <v>11007</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14948,7 +14948,7 @@
         <v>11987</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14989,7 +14989,7 @@
         <v>9991</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15030,7 +15030,7 @@
         <v>8952</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15071,7 +15071,7 @@
         <v>10575</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15112,7 +15112,7 @@
         <v>10855</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15153,7 +15153,7 @@
         <v>8651</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15194,7 +15194,7 @@
         <v>9010</v>
       </c>
       <c r="M71" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15235,7 +15235,7 @@
         <v>7961</v>
       </c>
       <c r="M72" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15276,7 +15276,7 @@
         <v>12011</v>
       </c>
       <c r="M73" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15317,7 +15317,7 @@
         <v>8177</v>
       </c>
       <c r="M74" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15358,7 +15358,7 @@
         <v>9158</v>
       </c>
       <c r="M75" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15399,7 +15399,7 @@
         <v>6938</v>
       </c>
       <c r="M76" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15440,7 +15440,7 @@
         <v>7734</v>
       </c>
       <c r="M77" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15481,7 +15481,7 @@
         <v>7602</v>
       </c>
       <c r="M78" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15522,7 +15522,7 @@
         <v>7450</v>
       </c>
       <c r="M79" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15563,7 +15563,7 @@
         <v>6987</v>
       </c>
       <c r="M80" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15604,7 +15604,7 @@
         <v>7114</v>
       </c>
       <c r="M81" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15645,7 +15645,7 @@
         <v>8655</v>
       </c>
       <c r="M82" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15686,7 +15686,7 @@
         <v>8239</v>
       </c>
       <c r="M83" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15727,7 +15727,7 @@
         <v>8021</v>
       </c>
       <c r="M84" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15768,7 +15768,7 @@
         <v>7480</v>
       </c>
       <c r="M85" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15809,7 +15809,7 @@
         <v>7087</v>
       </c>
       <c r="M86" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15850,7 +15850,7 @@
         <v>6846</v>
       </c>
       <c r="M87" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15891,7 +15891,7 @@
         <v>6106</v>
       </c>
       <c r="M88" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15932,7 +15932,7 @@
         <v>5490</v>
       </c>
       <c r="M89" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15973,7 +15973,7 @@
         <v>6535</v>
       </c>
       <c r="M90" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16014,7 +16014,7 @@
         <v>6366</v>
       </c>
       <c r="M91" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16055,7 +16055,7 @@
         <v>6623</v>
       </c>
       <c r="M92" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16096,7 +16096,7 @@
         <v>6429</v>
       </c>
       <c r="M93" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16137,7 +16137,7 @@
         <v>6712</v>
       </c>
       <c r="M94" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16178,7 +16178,7 @@
         <v>6524</v>
       </c>
       <c r="M95" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16219,7 +16219,7 @@
         <v>7611</v>
       </c>
       <c r="M96" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16260,7 +16260,7 @@
         <v>7530</v>
       </c>
       <c r="M97" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16301,7 +16301,7 @@
         <v>5552</v>
       </c>
       <c r="M98" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16342,7 +16342,7 @@
         <v>5036</v>
       </c>
       <c r="M99" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16383,7 +16383,7 @@
         <v>1515</v>
       </c>
       <c r="M100" s="3" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/wealthscale/WealthScale_201_Pages_Index.xlsx
+++ b/wealthscale/WealthScale_201_Pages_Index.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2626" uniqueCount="1739">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2626" uniqueCount="1740">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -126,96 +126,99 @@
     <t xml:space="preserve">pages-paste/102-tax.html</t>
   </si>
   <si>
+    <t xml:space="preserve">Done</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://wealthscale.ca/calculators/income-tax-calculator/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/calculators/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Income Tax Calculator Canada 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Income Tax Calculator Canada 2026: Federal and Provincial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Income tax calculator Canada 2026: federal and provincial tax, average and marginal rates in all 13 regions. $80,000 in Ontario pays $15,497.25.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">income tax calculator canada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canada tax calculator 2026, how much tax do i pay, marginal tax rate calculator, average tax rate canada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">calculator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">income-tax, take-home-pay, rrsp-refund, table-filter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pages-paste/103-calculators-income-tax-calculator.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://wealthscale.ca/tax/federal-tax-brackets/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/tax/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal Tax Brackets 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal Tax Brackets 2026: Canada's 14% to 33% Rates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal tax brackets 2026: 14% up to $58,523, then 20.5%, 26%, 29% and 33% over $258,482, with a $16,452 basic personal amount. See tax at any income.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">federal tax brackets 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">federal income tax rates 2026, canada tax brackets 2026, federal basic personal amount 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tax-guide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">income-tax, take-home-pay, rrsp-refund</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pages-paste/104-tax-federal-tax-brackets.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://wealthscale.ca/tax/marginal-tax-rates/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marginal Tax Rates in Canada 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marginal Tax Rates in Canada 2026 by Province</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marginal Tax Rate Canada 2026: Every Province Compared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marginal tax rate Canada 2026: combined federal and provincial rates at every bracket edge, top rates of 44.50% to 54.80%, and gain and dividend rates.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">marginal tax rate canada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">combined marginal tax rates 2026, top marginal tax rate canada, marginal tax rate ontario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">income-tax, capital-gains, dividend-tax, rrsp-refund</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pages-paste/105-tax-marginal-tax-rates.html</t>
+  </si>
+  <si>
     <t xml:space="preserve">Not started</t>
   </si>
   <si>
-    <t xml:space="preserve">https://wealthscale.ca/calculators/income-tax-calculator/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/calculators/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Income Tax Calculator Canada 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Income Tax Calculator Canada 2026: Federal and Provincial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Income tax calculator Canada 2026: federal and provincial tax, average and marginal rates in all 13 regions. $80,000 in Ontario pays $15,497.25.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">income tax calculator canada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canada tax calculator 2026, how much tax do i pay, marginal tax rate calculator, average tax rate canada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">calculator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">income-tax, take-home-pay, rrsp-refund, table-filter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pages-paste/103-calculators-income-tax-calculator.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://wealthscale.ca/tax/federal-tax-brackets/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/tax/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal Tax Brackets 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal Tax Brackets 2026: Canada's 14% to 33% Rates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal tax brackets 2026: 14% up to $58,523, then 20.5%, 26%, 29% and 33% over $258,482, with a $16,452 basic personal amount. See tax at any income.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">federal tax brackets 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">federal income tax rates 2026, canada tax brackets 2026, federal basic personal amount 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tax-guide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">income-tax, take-home-pay, rrsp-refund</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pages-paste/104-tax-federal-tax-brackets.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://wealthscale.ca/tax/marginal-tax-rates/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marginal Tax Rates in Canada 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marginal Tax Rates in Canada 2026 by Province</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marginal Tax Rate Canada 2026: Every Province Compared</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marginal tax rate Canada 2026: combined federal and provincial rates at every bracket edge, top rates of 44.50% to 54.80%, and gain and dividend rates.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">marginal tax rate canada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">combined marginal tax rates 2026, top marginal tax rate canada, marginal tax rate ontario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">income-tax, capital-gains, dividend-tax, rrsp-refund</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pages-paste/105-tax-marginal-tax-rates.html</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://wealthscale.ca/tax/ontario-tax-brackets/</t>
   </si>
   <si>
@@ -2754,9 +2757,6 @@
     <t xml:space="preserve">investment fee calculator</t>
   </si>
   <si>
-    <t xml:space="preserve">Done</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://wealthscale.ca/compare/best-brokers-for-dividend-investing/</t>
   </si>
   <si>
@@ -5145,13 +5145,16 @@
     <t xml:space="preserve">Rules are worded generally on the pages; confirm or ask for a change before Day 6.</t>
   </si>
   <si>
+    <t xml:space="preserve">Open (Navneet approved publishing Day 6 on October 30 before the review)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 dividend tax credit rates are not yet verified for Alberta, Saskatchewan, Manitoba, Yukon, the Northwest Territories and Nunavut. Pages and calculators show 'being confirmed' for these six.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adding the six rates turns dividend figures on for every province.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 dividend tax credit rates are not yet verified for Alberta, Saskatchewan, Manitoba, Yukon, the Northwest Territories and Nunavut. Pages and calculators show 'being confirmed' for these six.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adding the six rates turns dividend figures on for every province.</t>
   </si>
   <si>
     <t xml:space="preserve">Pages state the 2026 tax-year dates set by the Income Tax Act: RRSP contributions by March 1, 2027 (the 60th day of 2027), most returns and all balances by April 30, 2027, and June 15, 2027 for the self-employed. The CRA has not yet published its important-dates page for the 2026 tax year.</t>
@@ -5818,7 +5821,9 @@
       <c r="S2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="T2" s="4"/>
+      <c r="T2" s="4" t="n">
+        <v>46325</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="n">
@@ -5880,7 +5885,9 @@
       <c r="S3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="T3" s="4"/>
+      <c r="T3" s="4" t="n">
+        <v>46325</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="n">
@@ -5942,7 +5949,9 @@
       <c r="S4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="T4" s="4"/>
+      <c r="T4" s="4" t="n">
+        <v>46325</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="n">
@@ -6002,7 +6011,7 @@
         <v>61</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T5" s="4"/>
     </row>
@@ -6017,56 +6026,58 @@
         <v>46325</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I6" s="3" t="n">
         <f aca="false">LEN(H6)</f>
         <v>58</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K6" s="3" t="n">
         <f aca="false">LEN(J6)</f>
         <v>145</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O6" s="3" t="s">
         <v>29</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q6" s="5" t="n">
         <v>7214</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="T6" s="4"/>
+      <c r="T6" s="4" t="n">
+        <v>46325</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="n">
@@ -6079,56 +6090,58 @@
         <v>46325</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I7" s="3" t="n">
         <f aca="false">LEN(H7)</f>
         <v>56</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K7" s="3" t="n">
         <f aca="false">LEN(J7)</f>
         <v>153</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O7" s="3" t="s">
         <v>29</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>6433</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="S7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="T7" s="4"/>
+      <c r="T7" s="4" t="n">
+        <v>46325</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="n">
@@ -6141,56 +6154,58 @@
         <v>46325</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I8" s="3" t="n">
         <f aca="false">LEN(H8)</f>
         <v>58</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K8" s="3" t="n">
         <f aca="false">LEN(J8)</f>
         <v>155</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>29</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>6005</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="S8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="T8" s="4"/>
+      <c r="T8" s="4" t="n">
+        <v>46325</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="n">
@@ -6203,56 +6218,58 @@
         <v>46325</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I9" s="3" t="n">
         <f aca="false">LEN(H9)</f>
         <v>57</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K9" s="3" t="n">
         <f aca="false">LEN(J9)</f>
         <v>149</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>29</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>6337</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="S9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="T9" s="4"/>
+      <c r="T9" s="4" t="n">
+        <v>46325</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="n">
@@ -6265,56 +6282,58 @@
         <v>46325</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I10" s="3" t="n">
         <f aca="false">LEN(H10)</f>
         <v>53</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K10" s="3" t="n">
         <f aca="false">LEN(J10)</f>
         <v>150</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>29</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>6459</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="S10" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="T10" s="4"/>
+      <c r="T10" s="4" t="n">
+        <v>46325</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="n">
@@ -6327,56 +6346,58 @@
         <v>46325</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I11" s="3" t="n">
         <f aca="false">LEN(H11)</f>
         <v>52</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K11" s="3" t="n">
         <f aca="false">LEN(J11)</f>
         <v>146</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O11" s="3" t="s">
         <v>29</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>5468</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S11" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="T11" s="4"/>
+      <c r="T11" s="4" t="n">
+        <v>46325</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="n">
@@ -6389,56 +6410,58 @@
         <v>46325</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I12" s="3" t="n">
         <f aca="false">LEN(H12)</f>
         <v>55</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K12" s="3" t="n">
         <f aca="false">LEN(J12)</f>
         <v>149</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>29</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>5439</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="S12" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="T12" s="4"/>
+      <c r="T12" s="4" t="n">
+        <v>46325</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="n">
@@ -6451,56 +6474,58 @@
         <v>46325</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I13" s="3" t="n">
         <f aca="false">LEN(H13)</f>
         <v>53</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K13" s="3" t="n">
         <f aca="false">LEN(J13)</f>
         <v>146</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O13" s="3" t="s">
         <v>29</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>5285</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="S13" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="T13" s="4"/>
+      <c r="T13" s="4" t="n">
+        <v>46325</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="n">
@@ -6513,56 +6538,58 @@
         <v>46325</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I14" s="3" t="n">
         <f aca="false">LEN(H14)</f>
         <v>55</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K14" s="3" t="n">
         <f aca="false">LEN(J14)</f>
         <v>149</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>29</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>5612</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="T14" s="4"/>
+      <c r="T14" s="4" t="n">
+        <v>46325</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="n">
@@ -6575,56 +6602,58 @@
         <v>46325</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I15" s="3" t="n">
         <f aca="false">LEN(H15)</f>
         <v>60</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K15" s="3" t="n">
         <f aca="false">LEN(J15)</f>
         <v>149</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>29</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>6953</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="T15" s="4"/>
+      <c r="T15" s="4" t="n">
+        <v>46325</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="n">
@@ -6637,56 +6666,58 @@
         <v>46325</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I16" s="3" t="n">
         <f aca="false">LEN(H16)</f>
         <v>55</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K16" s="3" t="n">
         <f aca="false">LEN(J16)</f>
         <v>145</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O16" s="3" t="s">
         <v>29</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>5990</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="S16" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="T16" s="4"/>
+      <c r="T16" s="4" t="n">
+        <v>46325</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="n">
@@ -6699,56 +6730,58 @@
         <v>46325</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I17" s="3" t="n">
         <f aca="false">LEN(H17)</f>
         <v>54</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K17" s="3" t="n">
         <f aca="false">LEN(J17)</f>
         <v>157</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O17" s="3" t="s">
         <v>29</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>5856</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="T17" s="4"/>
+      <c r="T17" s="4" t="n">
+        <v>46325</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="n">
@@ -6761,56 +6794,58 @@
         <v>46325</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I18" s="3" t="n">
         <f aca="false">LEN(H18)</f>
         <v>51</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K18" s="3" t="n">
         <f aca="false">LEN(J18)</f>
         <v>155</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>13779</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="T18" s="4"/>
+      <c r="T18" s="4" t="n">
+        <v>46325</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="n">
@@ -6823,56 +6858,58 @@
         <v>46325</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I19" s="3" t="n">
         <f aca="false">LEN(H19)</f>
         <v>56</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K19" s="3" t="n">
         <f aca="false">LEN(J19)</f>
         <v>153</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>9893</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="S19" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="T19" s="4"/>
+      <c r="T19" s="4" t="n">
+        <v>46325</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="n">
@@ -6885,56 +6922,58 @@
         <v>46325</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I20" s="3" t="n">
         <f aca="false">LEN(H20)</f>
         <v>56</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K20" s="3" t="n">
         <f aca="false">LEN(J20)</f>
         <v>148</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>12922</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="T20" s="4"/>
+      <c r="T20" s="4" t="n">
+        <v>46325</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="n">
@@ -6947,56 +6986,58 @@
         <v>46325</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I21" s="3" t="n">
         <f aca="false">LEN(H21)</f>
         <v>60</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K21" s="3" t="n">
         <f aca="false">LEN(J21)</f>
         <v>149</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q21" s="5" t="n">
         <v>8013</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="T21" s="4"/>
+      <c r="T21" s="4" t="n">
+        <v>46325</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="n">
@@ -7009,54 +7050,54 @@
         <v>46326</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I22" s="3" t="n">
         <f aca="false">LEN(H22)</f>
         <v>55</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K22" s="3" t="n">
         <f aca="false">LEN(J22)</f>
         <v>141</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>29</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>5644</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T22" s="4"/>
     </row>
@@ -7071,36 +7112,36 @@
         <v>46326</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I23" s="3" t="n">
         <f aca="false">LEN(H23)</f>
         <v>54</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K23" s="3" t="n">
         <f aca="false">LEN(J23)</f>
         <v>152</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N23" s="3" t="s">
         <v>50</v>
@@ -7109,16 +7150,16 @@
         <v>29</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q23" s="5" t="n">
         <v>5253</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T23" s="4"/>
     </row>
@@ -7133,36 +7174,36 @@
         <v>46326</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I24" s="3" t="n">
         <f aca="false">LEN(H24)</f>
         <v>54</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K24" s="3" t="n">
         <f aca="false">LEN(J24)</f>
         <v>143</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>40</v>
@@ -7171,16 +7212,16 @@
         <v>29</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q24" s="5" t="n">
         <v>5505</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T24" s="4"/>
     </row>
@@ -7195,36 +7236,36 @@
         <v>46326</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I25" s="3" t="n">
         <f aca="false">LEN(H25)</f>
         <v>59</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K25" s="3" t="n">
         <f aca="false">LEN(J25)</f>
         <v>155</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N25" s="3" t="s">
         <v>50</v>
@@ -7233,16 +7274,16 @@
         <v>29</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q25" s="5" t="n">
         <v>5983</v>
       </c>
       <c r="R25" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T25" s="4"/>
     </row>
@@ -7257,36 +7298,36 @@
         <v>46326</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I26" s="3" t="n">
         <f aca="false">LEN(H26)</f>
         <v>56</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K26" s="3" t="n">
         <f aca="false">LEN(J26)</f>
         <v>155</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>50</v>
@@ -7295,16 +7336,16 @@
         <v>29</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q26" s="5" t="n">
         <v>5477</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T26" s="4"/>
     </row>
@@ -7319,36 +7360,36 @@
         <v>46326</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I27" s="3" t="n">
         <f aca="false">LEN(H27)</f>
         <v>55</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K27" s="3" t="n">
         <f aca="false">LEN(J27)</f>
         <v>148</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N27" s="3" t="s">
         <v>50</v>
@@ -7357,16 +7398,16 @@
         <v>29</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q27" s="5" t="n">
         <v>5389</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T27" s="4"/>
     </row>
@@ -7381,36 +7422,36 @@
         <v>46326</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I28" s="3" t="n">
         <f aca="false">LEN(H28)</f>
         <v>52</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K28" s="3" t="n">
         <f aca="false">LEN(J28)</f>
         <v>153</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N28" s="3" t="s">
         <v>50</v>
@@ -7419,16 +7460,16 @@
         <v>29</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q28" s="5" t="n">
         <v>5074</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T28" s="4"/>
     </row>
@@ -7443,36 +7484,36 @@
         <v>46326</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I29" s="3" t="n">
         <f aca="false">LEN(H29)</f>
         <v>55</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K29" s="3" t="n">
         <f aca="false">LEN(J29)</f>
         <v>152</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>50</v>
@@ -7481,16 +7522,16 @@
         <v>29</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q29" s="5" t="n">
         <v>5911</v>
       </c>
       <c r="R29" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T29" s="4"/>
     </row>
@@ -7505,36 +7546,36 @@
         <v>46326</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I30" s="3" t="n">
         <f aca="false">LEN(H30)</f>
         <v>60</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K30" s="3" t="n">
         <f aca="false">LEN(J30)</f>
         <v>149</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N30" s="3" t="s">
         <v>50</v>
@@ -7543,16 +7584,16 @@
         <v>29</v>
       </c>
       <c r="P30" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q30" s="5" t="n">
         <v>6062</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T30" s="4"/>
     </row>
@@ -7567,36 +7608,36 @@
         <v>46326</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="I31" s="3" t="n">
         <f aca="false">LEN(H31)</f>
         <v>51</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K31" s="3" t="n">
         <f aca="false">LEN(J31)</f>
         <v>150</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N31" s="3" t="s">
         <v>50</v>
@@ -7605,16 +7646,16 @@
         <v>29</v>
       </c>
       <c r="P31" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q31" s="5" t="n">
         <v>6210</v>
       </c>
       <c r="R31" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T31" s="4"/>
     </row>
@@ -7629,36 +7670,36 @@
         <v>46326</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="I32" s="3" t="n">
         <f aca="false">LEN(H32)</f>
         <v>59</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K32" s="3" t="n">
         <f aca="false">LEN(J32)</f>
         <v>151</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>50</v>
@@ -7667,16 +7708,16 @@
         <v>29</v>
       </c>
       <c r="P32" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q32" s="5" t="n">
         <v>5177</v>
       </c>
       <c r="R32" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="S32" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T32" s="4"/>
     </row>
@@ -7691,36 +7732,36 @@
         <v>46326</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="I33" s="3" t="n">
         <f aca="false">LEN(H33)</f>
         <v>57</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K33" s="3" t="n">
         <f aca="false">LEN(J33)</f>
         <v>147</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N33" s="3" t="s">
         <v>50</v>
@@ -7729,16 +7770,16 @@
         <v>29</v>
       </c>
       <c r="P33" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q33" s="5" t="n">
         <v>7058</v>
       </c>
       <c r="R33" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="S33" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T33" s="4"/>
     </row>
@@ -7753,54 +7794,54 @@
         <v>46326</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="I34" s="3" t="n">
         <f aca="false">LEN(H34)</f>
         <v>52</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K34" s="3" t="n">
         <f aca="false">LEN(J34)</f>
         <v>153</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P34" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q34" s="5" t="n">
         <v>6574</v>
       </c>
       <c r="R34" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="S34" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T34" s="4"/>
     </row>
@@ -7815,54 +7856,54 @@
         <v>46326</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I35" s="3" t="n">
         <f aca="false">LEN(H35)</f>
         <v>55</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K35" s="3" t="n">
         <f aca="false">LEN(J35)</f>
         <v>155</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q35" s="5" t="n">
         <v>6482</v>
       </c>
       <c r="R35" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="S35" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T35" s="4"/>
     </row>
@@ -7877,54 +7918,54 @@
         <v>46326</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="I36" s="3" t="n">
         <f aca="false">LEN(H36)</f>
         <v>52</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K36" s="3" t="n">
         <f aca="false">LEN(J36)</f>
         <v>152</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P36" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q36" s="5" t="n">
         <v>6672</v>
       </c>
       <c r="R36" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="S36" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T36" s="4"/>
     </row>
@@ -7939,54 +7980,54 @@
         <v>46326</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="I37" s="3" t="n">
         <f aca="false">LEN(H37)</f>
         <v>60</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K37" s="3" t="n">
         <f aca="false">LEN(J37)</f>
         <v>150</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q37" s="5" t="n">
         <v>7622</v>
       </c>
       <c r="R37" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="S37" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T37" s="4"/>
     </row>
@@ -8001,54 +8042,54 @@
         <v>46326</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I38" s="3" t="n">
         <f aca="false">LEN(H38)</f>
         <v>58</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K38" s="3" t="n">
         <f aca="false">LEN(J38)</f>
         <v>146</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N38" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P38" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q38" s="5" t="n">
         <v>6954</v>
       </c>
       <c r="R38" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="S38" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T38" s="4"/>
     </row>
@@ -8063,54 +8104,54 @@
         <v>46326</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="I39" s="3" t="n">
         <f aca="false">LEN(H39)</f>
         <v>52</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K39" s="3" t="n">
         <f aca="false">LEN(J39)</f>
         <v>154</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N39" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q39" s="5" t="n">
         <v>11892</v>
       </c>
       <c r="R39" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="S39" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T39" s="4"/>
     </row>
@@ -8125,54 +8166,54 @@
         <v>46326</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I40" s="3" t="n">
         <f aca="false">LEN(H40)</f>
         <v>57</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K40" s="3" t="n">
         <f aca="false">LEN(J40)</f>
         <v>155</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N40" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P40" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q40" s="5" t="n">
         <v>11227</v>
       </c>
       <c r="R40" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="S40" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T40" s="4"/>
     </row>
@@ -8187,54 +8228,54 @@
         <v>46326</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="I41" s="3" t="n">
         <f aca="false">LEN(H41)</f>
         <v>54</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K41" s="3" t="n">
         <f aca="false">LEN(J41)</f>
         <v>150</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O41" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P41" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q41" s="5" t="n">
         <v>9179</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="S41" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T41" s="4"/>
     </row>
@@ -8249,54 +8290,54 @@
         <v>46327</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I42" s="3" t="n">
         <f aca="false">LEN(H42)</f>
         <v>60</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="K42" s="3" t="n">
         <f aca="false">LEN(J42)</f>
         <v>153</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N42" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O42" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P42" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q42" s="5" t="n">
         <v>7138</v>
       </c>
       <c r="R42" s="3" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="S42" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T42" s="4"/>
     </row>
@@ -8311,54 +8352,54 @@
         <v>46327</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I43" s="3" t="n">
         <f aca="false">LEN(H43)</f>
         <v>54</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K43" s="3" t="n">
         <f aca="false">LEN(J43)</f>
         <v>151</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O43" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P43" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q43" s="5" t="n">
         <v>7722</v>
       </c>
       <c r="R43" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="S43" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T43" s="4"/>
     </row>
@@ -8373,54 +8414,54 @@
         <v>46327</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="I44" s="3" t="n">
         <f aca="false">LEN(H44)</f>
         <v>51</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K44" s="3" t="n">
         <f aca="false">LEN(J44)</f>
         <v>142</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N44" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O44" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P44" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q44" s="5" t="n">
         <v>7088</v>
       </c>
       <c r="R44" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="S44" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T44" s="4"/>
     </row>
@@ -8435,54 +8476,54 @@
         <v>46327</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="I45" s="3" t="n">
         <f aca="false">LEN(H45)</f>
         <v>50</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K45" s="3" t="n">
         <f aca="false">LEN(J45)</f>
         <v>150</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N45" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O45" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q45" s="5" t="n">
         <v>6784</v>
       </c>
       <c r="R45" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="S45" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T45" s="4"/>
     </row>
@@ -8497,54 +8538,54 @@
         <v>46327</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="I46" s="3" t="n">
         <f aca="false">LEN(H46)</f>
         <v>57</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K46" s="3" t="n">
         <f aca="false">LEN(J46)</f>
         <v>154</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N46" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O46" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P46" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q46" s="5" t="n">
         <v>5679</v>
       </c>
       <c r="R46" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="S46" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T46" s="4"/>
     </row>
@@ -8559,54 +8600,54 @@
         <v>46327</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="I47" s="3" t="n">
         <f aca="false">LEN(H47)</f>
         <v>58</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K47" s="3" t="n">
         <f aca="false">LEN(J47)</f>
         <v>151</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O47" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Q47" s="5" t="n">
         <v>7181</v>
       </c>
       <c r="R47" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="S47" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T47" s="4"/>
     </row>
@@ -8621,54 +8662,54 @@
         <v>46327</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="I48" s="3" t="n">
         <f aca="false">LEN(H48)</f>
         <v>57</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K48" s="3" t="n">
         <f aca="false">LEN(J48)</f>
         <v>148</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N48" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O48" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P48" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Q48" s="5" t="n">
         <v>6929</v>
       </c>
       <c r="R48" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="S48" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T48" s="4"/>
     </row>
@@ -8683,54 +8724,54 @@
         <v>46327</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="I49" s="3" t="n">
         <f aca="false">LEN(H49)</f>
         <v>55</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K49" s="3" t="n">
         <f aca="false">LEN(J49)</f>
         <v>154</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O49" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P49" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Q49" s="5" t="n">
         <v>7774</v>
       </c>
       <c r="R49" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="S49" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T49" s="4"/>
     </row>
@@ -8745,54 +8786,54 @@
         <v>46327</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="I50" s="3" t="n">
         <f aca="false">LEN(H50)</f>
         <v>52</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K50" s="3" t="n">
         <f aca="false">LEN(J50)</f>
         <v>154</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O50" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P50" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Q50" s="5" t="n">
         <v>6800</v>
       </c>
       <c r="R50" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="S50" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T50" s="4"/>
     </row>
@@ -8807,54 +8848,54 @@
         <v>46327</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="I51" s="3" t="n">
         <f aca="false">LEN(H51)</f>
         <v>58</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="K51" s="3" t="n">
         <f aca="false">LEN(J51)</f>
         <v>154</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N51" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Q51" s="5" t="n">
         <v>7270</v>
       </c>
       <c r="R51" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="S51" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T51" s="4"/>
     </row>
@@ -8869,54 +8910,54 @@
         <v>46327</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="I52" s="3" t="n">
         <f aca="false">LEN(H52)</f>
         <v>58</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="K52" s="3" t="n">
         <f aca="false">LEN(J52)</f>
         <v>147</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O52" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P52" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Q52" s="5" t="n">
         <v>6737</v>
       </c>
       <c r="R52" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="S52" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T52" s="4"/>
     </row>
@@ -8931,54 +8972,54 @@
         <v>46327</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="I53" s="3" t="n">
         <f aca="false">LEN(H53)</f>
         <v>58</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="K53" s="3" t="n">
         <f aca="false">LEN(J53)</f>
         <v>148</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="Q53" s="5" t="n">
         <v>6992</v>
       </c>
       <c r="R53" s="3" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="S53" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T53" s="4"/>
     </row>
@@ -8993,54 +9034,54 @@
         <v>46327</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="I54" s="3" t="n">
         <f aca="false">LEN(H54)</f>
         <v>54</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K54" s="3" t="n">
         <f aca="false">LEN(J54)</f>
         <v>154</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N54" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O54" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P54" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="Q54" s="5" t="n">
         <v>7445</v>
       </c>
       <c r="R54" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="S54" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T54" s="4"/>
     </row>
@@ -9055,54 +9096,54 @@
         <v>46327</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="I55" s="3" t="n">
         <f aca="false">LEN(H55)</f>
         <v>57</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K55" s="3" t="n">
         <f aca="false">LEN(J55)</f>
         <v>151</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N55" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O55" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P55" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="Q55" s="5" t="n">
         <v>6289</v>
       </c>
       <c r="R55" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="S55" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T55" s="4"/>
     </row>
@@ -9117,54 +9158,54 @@
         <v>46327</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="I56" s="3" t="n">
         <f aca="false">LEN(H56)</f>
         <v>56</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="K56" s="3" t="n">
         <f aca="false">LEN(J56)</f>
         <v>149</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N56" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O56" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P56" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Q56" s="5" t="n">
         <v>6298</v>
       </c>
       <c r="R56" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="S56" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T56" s="4"/>
     </row>
@@ -9179,36 +9220,36 @@
         <v>46327</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="I57" s="3" t="n">
         <f aca="false">LEN(H57)</f>
         <v>57</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="K57" s="3" t="n">
         <f aca="false">LEN(J57)</f>
         <v>149</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>50</v>
@@ -9217,16 +9258,16 @@
         <v>29</v>
       </c>
       <c r="P57" s="3" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="Q57" s="5" t="n">
         <v>6476</v>
       </c>
       <c r="R57" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="S57" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T57" s="4"/>
     </row>
@@ -9241,54 +9282,54 @@
         <v>46327</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="I58" s="3" t="n">
         <f aca="false">LEN(H58)</f>
         <v>59</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="K58" s="3" t="n">
         <f aca="false">LEN(J58)</f>
         <v>145</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N58" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>29</v>
       </c>
       <c r="P58" s="3" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="Q58" s="5" t="n">
         <v>6110</v>
       </c>
       <c r="R58" s="3" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="S58" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T58" s="4"/>
     </row>
@@ -9303,54 +9344,54 @@
         <v>46327</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="I59" s="3" t="n">
         <f aca="false">LEN(H59)</f>
         <v>55</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="K59" s="3" t="n">
         <f aca="false">LEN(J59)</f>
         <v>149</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N59" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O59" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P59" s="3" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="Q59" s="5" t="n">
         <v>12495</v>
       </c>
       <c r="R59" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="S59" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T59" s="4"/>
     </row>
@@ -9365,54 +9406,54 @@
         <v>46327</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="I60" s="3" t="n">
         <f aca="false">LEN(H60)</f>
         <v>57</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="K60" s="3" t="n">
         <f aca="false">LEN(J60)</f>
         <v>148</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N60" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O60" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P60" s="3" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="Q60" s="5" t="n">
         <v>8289</v>
       </c>
       <c r="R60" s="3" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="S60" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T60" s="4"/>
     </row>
@@ -9427,54 +9468,54 @@
         <v>46327</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="I61" s="3" t="n">
         <f aca="false">LEN(H61)</f>
         <v>55</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="K61" s="3" t="n">
         <f aca="false">LEN(J61)</f>
         <v>150</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N61" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O61" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P61" s="3" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="Q61" s="5" t="n">
         <v>8422</v>
       </c>
       <c r="R61" s="3" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="S61" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T61" s="4"/>
     </row>
@@ -9489,54 +9530,54 @@
         <v>46328</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="I62" s="3" t="n">
         <f aca="false">LEN(H62)</f>
         <v>59</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="K62" s="3" t="n">
         <f aca="false">LEN(J62)</f>
         <v>148</v>
       </c>
       <c r="L62" s="3" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N62" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>29</v>
       </c>
       <c r="P62" s="3" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="Q62" s="5" t="n">
         <v>6491</v>
       </c>
       <c r="R62" s="3" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="S62" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T62" s="4"/>
     </row>
@@ -9551,54 +9592,54 @@
         <v>46328</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="I63" s="3" t="n">
         <f aca="false">LEN(H63)</f>
         <v>56</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="K63" s="3" t="n">
         <f aca="false">LEN(J63)</f>
         <v>152</v>
       </c>
       <c r="L63" s="3" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N63" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O63" s="3" t="s">
         <v>29</v>
       </c>
       <c r="P63" s="3" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="Q63" s="5" t="n">
         <v>5930</v>
       </c>
       <c r="R63" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="S63" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T63" s="4"/>
     </row>
@@ -9613,54 +9654,54 @@
         <v>46328</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I64" s="3" t="n">
         <f aca="false">LEN(H64)</f>
         <v>57</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="K64" s="3" t="n">
         <f aca="false">LEN(J64)</f>
         <v>152</v>
       </c>
       <c r="L64" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N64" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O64" s="3" t="s">
         <v>29</v>
       </c>
       <c r="P64" s="3" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="Q64" s="5" t="n">
         <v>5901</v>
       </c>
       <c r="R64" s="3" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="S64" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T64" s="4"/>
     </row>
@@ -9675,54 +9716,54 @@
         <v>46328</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="I65" s="3" t="n">
         <f aca="false">LEN(H65)</f>
         <v>55</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="K65" s="3" t="n">
         <f aca="false">LEN(J65)</f>
         <v>150</v>
       </c>
       <c r="L65" s="3" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N65" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O65" s="3" t="s">
         <v>29</v>
       </c>
       <c r="P65" s="3" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="Q65" s="5" t="n">
         <v>6494</v>
       </c>
       <c r="R65" s="3" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="S65" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T65" s="4"/>
     </row>
@@ -9737,36 +9778,36 @@
         <v>46328</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="I66" s="3" t="n">
         <f aca="false">LEN(H66)</f>
         <v>55</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="K66" s="3" t="n">
         <f aca="false">LEN(J66)</f>
         <v>150</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N66" s="3" t="s">
         <v>40</v>
@@ -9775,16 +9816,16 @@
         <v>29</v>
       </c>
       <c r="P66" s="3" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="Q66" s="5" t="n">
         <v>4794</v>
       </c>
       <c r="R66" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="S66" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T66" s="4"/>
     </row>
@@ -9799,36 +9840,36 @@
         <v>46328</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="I67" s="3" t="n">
         <f aca="false">LEN(H67)</f>
         <v>51</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="K67" s="3" t="n">
         <f aca="false">LEN(J67)</f>
         <v>146</v>
       </c>
       <c r="L67" s="3" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="N67" s="3" t="s">
         <v>40</v>
@@ -9837,16 +9878,16 @@
         <v>29</v>
       </c>
       <c r="P67" s="3" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="Q67" s="5" t="n">
         <v>3748</v>
       </c>
       <c r="R67" s="3" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="S67" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T67" s="4"/>
     </row>
@@ -9861,54 +9902,54 @@
         <v>46328</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I68" s="3" t="n">
         <f aca="false">LEN(H68)</f>
         <v>55</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="K68" s="3" t="n">
         <f aca="false">LEN(J68)</f>
         <v>154</v>
       </c>
       <c r="L68" s="3" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N68" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O68" s="3" t="s">
         <v>29</v>
       </c>
       <c r="P68" s="3" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="Q68" s="5" t="n">
         <v>5650</v>
       </c>
       <c r="R68" s="3" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="S68" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T68" s="4"/>
     </row>
@@ -9923,54 +9964,54 @@
         <v>46328</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="I69" s="3" t="n">
         <f aca="false">LEN(H69)</f>
         <v>56</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="K69" s="3" t="n">
         <f aca="false">LEN(J69)</f>
         <v>155</v>
       </c>
       <c r="L69" s="3" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="N69" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O69" s="3" t="s">
         <v>29</v>
       </c>
       <c r="P69" s="3" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="Q69" s="5" t="n">
         <v>6186</v>
       </c>
       <c r="R69" s="3" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="S69" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T69" s="4"/>
     </row>
@@ -9985,54 +10026,54 @@
         <v>46328</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="I70" s="3" t="n">
         <f aca="false">LEN(H70)</f>
         <v>58</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="K70" s="3" t="n">
         <f aca="false">LEN(J70)</f>
         <v>154</v>
       </c>
       <c r="L70" s="3" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="N70" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O70" s="3" t="s">
         <v>29</v>
       </c>
       <c r="P70" s="3" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="Q70" s="5" t="n">
         <v>5562</v>
       </c>
       <c r="R70" s="3" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="S70" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T70" s="4"/>
     </row>
@@ -10047,54 +10088,54 @@
         <v>46328</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="I71" s="3" t="n">
         <f aca="false">LEN(H71)</f>
         <v>60</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="K71" s="3" t="n">
         <f aca="false">LEN(J71)</f>
         <v>151</v>
       </c>
       <c r="L71" s="3" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="M71" s="3" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="N71" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O71" s="3" t="s">
         <v>29</v>
       </c>
       <c r="P71" s="3" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="Q71" s="5" t="n">
         <v>5380</v>
       </c>
       <c r="R71" s="3" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="S71" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T71" s="4"/>
     </row>
@@ -10109,54 +10150,54 @@
         <v>46328</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="I72" s="3" t="n">
         <f aca="false">LEN(H72)</f>
         <v>59</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="K72" s="3" t="n">
         <f aca="false">LEN(J72)</f>
         <v>144</v>
       </c>
       <c r="L72" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="M72" s="3" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="N72" s="3" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>29</v>
       </c>
       <c r="P72" s="3" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="Q72" s="5" t="n">
         <v>4737</v>
       </c>
       <c r="R72" s="3" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="S72" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T72" s="4"/>
     </row>
@@ -10171,54 +10212,54 @@
         <v>46328</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="I73" s="3" t="n">
         <f aca="false">LEN(H73)</f>
         <v>53</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="K73" s="3" t="n">
         <f aca="false">LEN(J73)</f>
         <v>153</v>
       </c>
       <c r="L73" s="3" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="M73" s="3" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="N73" s="3" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="O73" s="3" t="s">
         <v>29</v>
       </c>
       <c r="P73" s="3" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="Q73" s="5" t="n">
         <v>4754</v>
       </c>
       <c r="R73" s="3" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="S73" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T73" s="4"/>
     </row>
@@ -10233,36 +10274,36 @@
         <v>46328</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="I74" s="3" t="n">
         <f aca="false">LEN(H74)</f>
         <v>57</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="K74" s="3" t="n">
         <f aca="false">LEN(J74)</f>
         <v>143</v>
       </c>
       <c r="L74" s="3" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="M74" s="3" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="N74" s="3" t="s">
         <v>40</v>
@@ -10271,16 +10312,16 @@
         <v>29</v>
       </c>
       <c r="P74" s="3" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="Q74" s="5" t="n">
         <v>5056</v>
       </c>
       <c r="R74" s="3" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="S74" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T74" s="4"/>
     </row>
@@ -10295,54 +10336,54 @@
         <v>46328</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="I75" s="3" t="n">
         <f aca="false">LEN(H75)</f>
         <v>57</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="K75" s="3" t="n">
         <f aca="false">LEN(J75)</f>
         <v>149</v>
       </c>
       <c r="L75" s="3" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M75" s="3" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N75" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O75" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P75" s="3" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="Q75" s="5" t="n">
         <v>4524</v>
       </c>
       <c r="R75" s="3" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="S75" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T75" s="4"/>
     </row>
@@ -10357,54 +10398,54 @@
         <v>46328</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="I76" s="3" t="n">
         <f aca="false">LEN(H76)</f>
         <v>59</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="K76" s="3" t="n">
         <f aca="false">LEN(J76)</f>
         <v>150</v>
       </c>
       <c r="L76" s="3" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="M76" s="3" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="N76" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O76" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P76" s="3" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="Q76" s="5" t="n">
         <v>4493</v>
       </c>
       <c r="R76" s="3" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="S76" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T76" s="4"/>
     </row>
@@ -10419,36 +10460,36 @@
         <v>46328</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="I77" s="3" t="n">
         <f aca="false">LEN(H77)</f>
         <v>59</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="K77" s="3" t="n">
         <f aca="false">LEN(J77)</f>
         <v>147</v>
       </c>
       <c r="L77" s="3" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="M77" s="3" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="N77" s="3" t="s">
         <v>40</v>
@@ -10457,16 +10498,16 @@
         <v>29</v>
       </c>
       <c r="P77" s="3" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="Q77" s="5" t="n">
         <v>4291</v>
       </c>
       <c r="R77" s="3" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="S77" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T77" s="4"/>
     </row>
@@ -10481,36 +10522,36 @@
         <v>46328</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="I78" s="3" t="n">
         <f aca="false">LEN(H78)</f>
         <v>55</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="K78" s="3" t="n">
         <f aca="false">LEN(J78)</f>
         <v>151</v>
       </c>
       <c r="L78" s="3" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M78" s="3" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="N78" s="3" t="s">
         <v>40</v>
@@ -10519,16 +10560,16 @@
         <v>29</v>
       </c>
       <c r="P78" s="3" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="Q78" s="5" t="n">
         <v>4076</v>
       </c>
       <c r="R78" s="3" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="S78" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T78" s="4"/>
     </row>
@@ -10543,54 +10584,54 @@
         <v>46328</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="I79" s="3" t="n">
         <f aca="false">LEN(H79)</f>
         <v>53</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="K79" s="3" t="n">
         <f aca="false">LEN(J79)</f>
         <v>140</v>
       </c>
       <c r="L79" s="3" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="M79" s="3" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="N79" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O79" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P79" s="3" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="Q79" s="5" t="n">
         <v>5683</v>
       </c>
       <c r="R79" s="3" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="S79" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T79" s="4"/>
     </row>
@@ -10605,54 +10646,54 @@
         <v>46328</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="I80" s="3" t="n">
         <f aca="false">LEN(H80)</f>
         <v>54</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="K80" s="3" t="n">
         <f aca="false">LEN(J80)</f>
         <v>152</v>
       </c>
       <c r="L80" s="3" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="M80" s="3" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="N80" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O80" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P80" s="3" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="Q80" s="5" t="n">
         <v>8618</v>
       </c>
       <c r="R80" s="3" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="S80" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T80" s="4"/>
     </row>
@@ -10667,54 +10708,54 @@
         <v>46328</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="I81" s="3" t="n">
         <f aca="false">LEN(H81)</f>
         <v>59</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="K81" s="3" t="n">
         <f aca="false">LEN(J81)</f>
         <v>144</v>
       </c>
       <c r="L81" s="3" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="M81" s="3" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="N81" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O81" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P81" s="3" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="Q81" s="5" t="n">
         <v>9280</v>
       </c>
       <c r="R81" s="3" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="S81" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T81" s="4"/>
     </row>
@@ -10729,54 +10770,54 @@
         <v>46329</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="I82" s="3" t="n">
         <f aca="false">LEN(H82)</f>
         <v>55</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="K82" s="3" t="n">
         <f aca="false">LEN(J82)</f>
         <v>147</v>
       </c>
       <c r="L82" s="3" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="M82" s="3" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="N82" s="3" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="O82" s="3" t="s">
         <v>29</v>
       </c>
       <c r="P82" s="3" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="Q82" s="5" t="n">
         <v>4809</v>
       </c>
       <c r="R82" s="3" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="S82" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T82" s="4"/>
     </row>
@@ -10791,36 +10832,36 @@
         <v>46329</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="I83" s="3" t="n">
         <f aca="false">LEN(H83)</f>
         <v>53</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="K83" s="3" t="n">
         <f aca="false">LEN(J83)</f>
         <v>141</v>
       </c>
       <c r="L83" s="3" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="M83" s="3" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>40</v>
@@ -10829,16 +10870,16 @@
         <v>29</v>
       </c>
       <c r="P83" s="3" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="Q83" s="5" t="n">
         <v>4158</v>
       </c>
       <c r="R83" s="3" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="S83" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T83" s="4"/>
     </row>
@@ -10853,36 +10894,36 @@
         <v>46329</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="I84" s="3" t="n">
         <f aca="false">LEN(H84)</f>
         <v>57</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="K84" s="3" t="n">
         <f aca="false">LEN(J84)</f>
         <v>146</v>
       </c>
       <c r="L84" s="3" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="M84" s="3" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="N84" s="3" t="s">
         <v>40</v>
@@ -10891,16 +10932,16 @@
         <v>29</v>
       </c>
       <c r="P84" s="3" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="Q84" s="5" t="n">
         <v>5594</v>
       </c>
       <c r="R84" s="3" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="S84" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T84" s="4"/>
     </row>
@@ -10915,36 +10956,36 @@
         <v>46329</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="I85" s="3" t="n">
         <f aca="false">LEN(H85)</f>
         <v>59</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="K85" s="3" t="n">
         <f aca="false">LEN(J85)</f>
         <v>145</v>
       </c>
       <c r="L85" s="3" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="M85" s="3" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="N85" s="3" t="s">
         <v>40</v>
@@ -10953,16 +10994,16 @@
         <v>29</v>
       </c>
       <c r="P85" s="3" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="Q85" s="5" t="n">
         <v>6040</v>
       </c>
       <c r="R85" s="3" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="S85" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T85" s="4"/>
     </row>
@@ -10977,36 +11018,36 @@
         <v>46329</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="I86" s="3" t="n">
         <f aca="false">LEN(H86)</f>
         <v>56</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="K86" s="3" t="n">
         <f aca="false">LEN(J86)</f>
         <v>151</v>
       </c>
       <c r="L86" s="3" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="M86" s="3" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="N86" s="3" t="s">
         <v>40</v>
@@ -11015,16 +11056,16 @@
         <v>29</v>
       </c>
       <c r="P86" s="3" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="Q86" s="5" t="n">
         <v>6068</v>
       </c>
       <c r="R86" s="3" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="S86" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T86" s="4"/>
     </row>
@@ -11039,36 +11080,36 @@
         <v>46329</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="I87" s="3" t="n">
         <f aca="false">LEN(H87)</f>
         <v>57</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="K87" s="3" t="n">
         <f aca="false">LEN(J87)</f>
         <v>151</v>
       </c>
       <c r="L87" s="3" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="M87" s="3" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="N87" s="3" t="s">
         <v>40</v>
@@ -11077,16 +11118,16 @@
         <v>29</v>
       </c>
       <c r="P87" s="3" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="Q87" s="5" t="n">
         <v>5077</v>
       </c>
       <c r="R87" s="3" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="S87" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T87" s="4"/>
     </row>
@@ -11101,54 +11142,54 @@
         <v>46329</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="I88" s="3" t="n">
         <f aca="false">LEN(H88)</f>
         <v>60</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="K88" s="3" t="n">
         <f aca="false">LEN(J88)</f>
         <v>150</v>
       </c>
       <c r="L88" s="3" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="M88" s="3" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="N88" s="3" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="O88" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P88" s="3" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="Q88" s="5" t="n">
         <v>8969</v>
       </c>
       <c r="R88" s="3" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="S88" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T88" s="4"/>
     </row>
@@ -11163,54 +11204,54 @@
         <v>46329</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="I89" s="3" t="n">
         <f aca="false">LEN(H89)</f>
         <v>54</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="K89" s="3" t="n">
         <f aca="false">LEN(J89)</f>
         <v>149</v>
       </c>
       <c r="L89" s="3" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="M89" s="3" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="N89" s="3" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="O89" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P89" s="3" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="Q89" s="5" t="n">
         <v>8081</v>
       </c>
       <c r="R89" s="3" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="S89" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T89" s="4"/>
     </row>
@@ -11225,54 +11266,54 @@
         <v>46329</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="I90" s="3" t="n">
         <f aca="false">LEN(H90)</f>
         <v>58</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="K90" s="3" t="n">
         <f aca="false">LEN(J90)</f>
         <v>155</v>
       </c>
       <c r="L90" s="3" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="M90" s="3" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="N90" s="3" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="O90" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P90" s="3" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="Q90" s="5" t="n">
         <v>7733</v>
       </c>
       <c r="R90" s="3" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="S90" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T90" s="4"/>
     </row>
@@ -11287,54 +11328,54 @@
         <v>46329</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="I91" s="3" t="n">
         <f aca="false">LEN(H91)</f>
         <v>58</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="K91" s="3" t="n">
         <f aca="false">LEN(J91)</f>
         <v>154</v>
       </c>
       <c r="L91" s="3" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="M91" s="3" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="N91" s="3" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="O91" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P91" s="3" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="Q91" s="5" t="n">
         <v>7222</v>
       </c>
       <c r="R91" s="3" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="S91" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T91" s="4"/>
     </row>
@@ -11349,54 +11390,54 @@
         <v>46329</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="I92" s="3" t="n">
         <f aca="false">LEN(H92)</f>
         <v>59</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="K92" s="3" t="n">
         <f aca="false">LEN(J92)</f>
         <v>149</v>
       </c>
       <c r="L92" s="3" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="M92" s="3" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="N92" s="3" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="O92" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P92" s="3" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="Q92" s="5" t="n">
         <v>7319</v>
       </c>
       <c r="R92" s="3" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="S92" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T92" s="4"/>
     </row>
@@ -11411,54 +11452,54 @@
         <v>46329</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="I93" s="3" t="n">
         <f aca="false">LEN(H93)</f>
         <v>57</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="K93" s="3" t="n">
         <f aca="false">LEN(J93)</f>
         <v>147</v>
       </c>
       <c r="L93" s="3" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="M93" s="3" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="N93" s="3" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="O93" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P93" s="3" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="Q93" s="5" t="n">
         <v>7098</v>
       </c>
       <c r="R93" s="3" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="S93" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T93" s="4"/>
     </row>
@@ -11473,54 +11514,54 @@
         <v>46329</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="I94" s="3" t="n">
         <f aca="false">LEN(H94)</f>
         <v>54</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="K94" s="3" t="n">
         <f aca="false">LEN(J94)</f>
         <v>151</v>
       </c>
       <c r="L94" s="3" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="M94" s="3" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="N94" s="3" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="O94" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P94" s="3" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="Q94" s="5" t="n">
         <v>7720</v>
       </c>
       <c r="R94" s="3" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="S94" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T94" s="4"/>
     </row>
@@ -11535,54 +11576,54 @@
         <v>46329</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="I95" s="3" t="n">
         <f aca="false">LEN(H95)</f>
         <v>54</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="K95" s="3" t="n">
         <f aca="false">LEN(J95)</f>
         <v>153</v>
       </c>
       <c r="L95" s="3" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="M95" s="3" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="N95" s="3" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="O95" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P95" s="3" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="Q95" s="5" t="n">
         <v>7267</v>
       </c>
       <c r="R95" s="3" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="S95" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T95" s="4"/>
     </row>
@@ -11597,54 +11638,54 @@
         <v>46329</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="I96" s="3" t="n">
         <f aca="false">LEN(H96)</f>
         <v>50</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="K96" s="3" t="n">
         <f aca="false">LEN(J96)</f>
         <v>149</v>
       </c>
       <c r="L96" s="3" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="M96" s="3" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="N96" s="3" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="O96" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P96" s="3" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="Q96" s="5" t="n">
         <v>6834</v>
       </c>
       <c r="R96" s="3" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="S96" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T96" s="4"/>
     </row>
@@ -11659,54 +11700,54 @@
         <v>46329</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="I97" s="3" t="n">
         <f aca="false">LEN(H97)</f>
         <v>53</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="K97" s="3" t="n">
         <f aca="false">LEN(J97)</f>
         <v>151</v>
       </c>
       <c r="L97" s="3" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="M97" s="3" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="N97" s="3" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="O97" s="3" t="s">
         <v>29</v>
       </c>
       <c r="P97" s="3" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="Q97" s="5" t="n">
         <v>6228</v>
       </c>
       <c r="R97" s="3" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="S97" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T97" s="4"/>
     </row>
@@ -11721,54 +11762,54 @@
         <v>46329</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="I98" s="3" t="n">
         <f aca="false">LEN(H98)</f>
         <v>58</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="K98" s="3" t="n">
         <f aca="false">LEN(J98)</f>
         <v>142</v>
       </c>
       <c r="L98" s="3" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="M98" s="3" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="N98" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O98" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P98" s="3" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="Q98" s="5" t="n">
         <v>10787</v>
       </c>
       <c r="R98" s="3" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="S98" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T98" s="4"/>
     </row>
@@ -11783,54 +11824,54 @@
         <v>46329</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="I99" s="3" t="n">
         <f aca="false">LEN(H99)</f>
         <v>56</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="K99" s="3" t="n">
         <f aca="false">LEN(J99)</f>
         <v>154</v>
       </c>
       <c r="L99" s="3" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="M99" s="3" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="N99" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O99" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P99" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q99" s="5" t="n">
         <v>10399</v>
       </c>
       <c r="R99" s="3" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="S99" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T99" s="4"/>
     </row>
@@ -11845,54 +11886,54 @@
         <v>46329</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="I100" s="3" t="n">
         <f aca="false">LEN(H100)</f>
         <v>56</v>
       </c>
       <c r="J100" s="3" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="K100" s="3" t="n">
         <f aca="false">LEN(J100)</f>
         <v>153</v>
       </c>
       <c r="L100" s="3" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="M100" s="3" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="N100" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O100" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P100" s="3" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="Q100" s="5" t="n">
         <v>8186</v>
       </c>
       <c r="R100" s="3" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="S100" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T100" s="4"/>
     </row>
@@ -11907,54 +11948,54 @@
         <v>46329</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="I101" s="3" t="n">
         <f aca="false">LEN(H101)</f>
         <v>53</v>
       </c>
       <c r="J101" s="3" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="K101" s="3" t="n">
         <f aca="false">LEN(J101)</f>
         <v>153</v>
       </c>
       <c r="L101" s="3" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="M101" s="3" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="N101" s="3" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>29</v>
       </c>
       <c r="P101" s="3" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="Q101" s="5" t="n">
         <v>6250</v>
       </c>
       <c r="R101" s="3" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="S101" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="T101" s="4"/>
     </row>
@@ -11999,19 +12040,19 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>16</v>
@@ -12019,13 +12060,13 @@
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B2" s="6" t="n">
         <v>46322</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D2" s="3" t="n">
         <f aca="false">COUNTIF('First 101 pages (latest)'!A$2:A$102,B2)</f>
@@ -12046,13 +12087,13 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B3" s="6" t="n">
         <v>46323</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="D3" s="3" t="n">
         <f aca="false">COUNTIF('First 101 pages (latest)'!A$2:A$102,B3)</f>
@@ -12073,13 +12114,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B4" s="6" t="n">
         <v>46324</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>0</v>
@@ -12102,19 +12143,19 @@
         <v>46325</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="D5" s="3" t="n">
         <f aca="false">COUNTIF(Pages!B$2:B$101,A5)</f>
         <v>20</v>
       </c>
       <c r="E5" s="3" t="n">
-        <f aca="false">COUNTIFS(Pages!B$2:B$101,A5,Pages!S$2:S$101,"Live")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Pages!B$2:B$101,A5,Pages!S$2:S$101,"Done")+COUNTIFS(Pages!B$2:B$101,A5,Pages!S$2:S$101,"Live")</f>
+        <v>19</v>
       </c>
       <c r="F5" s="3" t="n">
         <f aca="false">D5-E5</f>
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G5" s="5" t="n">
         <f aca="false">SUMIF(Pages!B$2:B$101,A5,Pages!Q$2:Q$101)</f>
@@ -12129,14 +12170,14 @@
         <v>46326</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="D6" s="3" t="n">
         <f aca="false">COUNTIF(Pages!B$2:B$101,A6)</f>
         <v>20</v>
       </c>
       <c r="E6" s="3" t="n">
-        <f aca="false">COUNTIFS(Pages!B$2:B$101,A6,Pages!S$2:S$101,"Live")</f>
+        <f aca="false">COUNTIFS(Pages!B$2:B$101,A6,Pages!S$2:S$101,"Done")+COUNTIFS(Pages!B$2:B$101,A6,Pages!S$2:S$101,"Live")</f>
         <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
@@ -12156,14 +12197,14 @@
         <v>46327</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="D7" s="3" t="n">
         <f aca="false">COUNTIF(Pages!B$2:B$101,A7)</f>
         <v>20</v>
       </c>
       <c r="E7" s="3" t="n">
-        <f aca="false">COUNTIFS(Pages!B$2:B$101,A7,Pages!S$2:S$101,"Live")</f>
+        <f aca="false">COUNTIFS(Pages!B$2:B$101,A7,Pages!S$2:S$101,"Done")+COUNTIFS(Pages!B$2:B$101,A7,Pages!S$2:S$101,"Live")</f>
         <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
@@ -12183,14 +12224,14 @@
         <v>46328</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="D8" s="3" t="n">
         <f aca="false">COUNTIF(Pages!B$2:B$101,A8)</f>
         <v>20</v>
       </c>
       <c r="E8" s="3" t="n">
-        <f aca="false">COUNTIFS(Pages!B$2:B$101,A8,Pages!S$2:S$101,"Live")</f>
+        <f aca="false">COUNTIFS(Pages!B$2:B$101,A8,Pages!S$2:S$101,"Done")+COUNTIFS(Pages!B$2:B$101,A8,Pages!S$2:S$101,"Live")</f>
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
@@ -12210,14 +12251,14 @@
         <v>46329</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="D9" s="3" t="n">
         <f aca="false">COUNTIF(Pages!B$2:B$101,A9)</f>
         <v>20</v>
       </c>
       <c r="E9" s="3" t="n">
-        <f aca="false">COUNTIFS(Pages!B$2:B$101,A9,Pages!S$2:S$101,"Live")</f>
+        <f aca="false">COUNTIFS(Pages!B$2:B$101,A9,Pages!S$2:S$101,"Done")+COUNTIFS(Pages!B$2:B$101,A9,Pages!S$2:S$101,"Live")</f>
         <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
@@ -12231,7 +12272,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="3"/>
@@ -12241,11 +12282,11 @@
       </c>
       <c r="E10" s="3" t="n">
         <f aca="false">SUM(E2:E9)</f>
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="F10" s="3" t="n">
         <f aca="false">SUM(F2:F9)</f>
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="G10" s="5" t="n">
         <f aca="false">SUM(G2:G9)</f>
@@ -12288,7 +12329,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -12297,10 +12338,10 @@
         <v>3</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>17</v>
@@ -12335,37 +12376,37 @@
         <v>27</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>29</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>34</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="L2" s="3" t="n">
         <v>8826</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12388,7 +12429,7 @@
         <v>911</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>912</v>
@@ -12406,7 +12447,7 @@
         <v>12564</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12429,7 +12470,7 @@
         <v>918</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>919</v>
@@ -12447,7 +12488,7 @@
         <v>8550</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12461,7 +12502,7 @@
         <v>923</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>924</v>
@@ -12488,7 +12529,7 @@
         <v>9033</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12502,7 +12543,7 @@
         <v>930</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>924</v>
@@ -12529,7 +12570,7 @@
         <v>2547</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12543,7 +12584,7 @@
         <v>936</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>924</v>
@@ -12570,7 +12611,7 @@
         <v>1634</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12584,7 +12625,7 @@
         <v>943</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>924</v>
@@ -12611,7 +12652,7 @@
         <v>2551</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12625,7 +12666,7 @@
         <v>949</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>924</v>
@@ -12652,7 +12693,7 @@
         <v>2109</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12666,7 +12707,7 @@
         <v>955</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>924</v>
@@ -12693,7 +12734,7 @@
         <v>1787</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12707,7 +12748,7 @@
         <v>961</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>924</v>
@@ -12734,7 +12775,7 @@
         <v>9923</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12748,7 +12789,7 @@
         <v>968</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>924</v>
@@ -12775,7 +12816,7 @@
         <v>6322</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12789,7 +12830,7 @@
         <v>974</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>924</v>
@@ -12816,7 +12857,7 @@
         <v>5924</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12830,7 +12871,7 @@
         <v>980</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>924</v>
@@ -12857,7 +12898,7 @@
         <v>4759</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12871,7 +12912,7 @@
         <v>986</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>924</v>
@@ -12898,7 +12939,7 @@
         <v>5468</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12912,7 +12953,7 @@
         <v>992</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>924</v>
@@ -12939,7 +12980,7 @@
         <v>4592</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12953,7 +12994,7 @@
         <v>998</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>924</v>
@@ -12980,7 +13021,7 @@
         <v>4676</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12994,7 +13035,7 @@
         <v>1004</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>924</v>
@@ -13021,7 +13062,7 @@
         <v>7146</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13035,7 +13076,7 @@
         <v>1010</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>924</v>
@@ -13062,7 +13103,7 @@
         <v>4377</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13076,7 +13117,7 @@
         <v>1016</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>924</v>
@@ -13103,7 +13144,7 @@
         <v>4066</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13117,7 +13158,7 @@
         <v>1022</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>924</v>
@@ -13144,7 +13185,7 @@
         <v>5160</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13158,7 +13199,7 @@
         <v>1028</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>924</v>
@@ -13185,7 +13226,7 @@
         <v>3971</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13199,7 +13240,7 @@
         <v>1034</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>924</v>
@@ -13226,7 +13267,7 @@
         <v>4256</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13240,7 +13281,7 @@
         <v>1040</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>924</v>
@@ -13267,7 +13308,7 @@
         <v>4177</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13281,7 +13322,7 @@
         <v>1046</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>924</v>
@@ -13308,7 +13349,7 @@
         <v>4223</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13322,7 +13363,7 @@
         <v>1052</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>924</v>
@@ -13349,7 +13390,7 @@
         <v>4204</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13363,7 +13404,7 @@
         <v>1058</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>924</v>
@@ -13390,7 +13431,7 @@
         <v>5486</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13404,7 +13445,7 @@
         <v>1064</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>924</v>
@@ -13431,7 +13472,7 @@
         <v>4744</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13445,7 +13486,7 @@
         <v>1070</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>924</v>
@@ -13454,7 +13495,7 @@
         <v>1071</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>1072</v>
@@ -13472,7 +13513,7 @@
         <v>7322</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13486,7 +13527,7 @@
         <v>1076</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>924</v>
@@ -13495,7 +13536,7 @@
         <v>1077</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>1078</v>
@@ -13513,7 +13554,7 @@
         <v>5845</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13527,7 +13568,7 @@
         <v>1082</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>924</v>
@@ -13536,7 +13577,7 @@
         <v>1083</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>1084</v>
@@ -13554,7 +13595,7 @@
         <v>5632</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13568,7 +13609,7 @@
         <v>1088</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>924</v>
@@ -13577,7 +13618,7 @@
         <v>1089</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>1090</v>
@@ -13595,7 +13636,7 @@
         <v>8708</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13609,7 +13650,7 @@
         <v>1094</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>924</v>
@@ -13618,7 +13659,7 @@
         <v>1095</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>1096</v>
@@ -13636,7 +13677,7 @@
         <v>7980</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13650,7 +13691,7 @@
         <v>1100</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>924</v>
@@ -13659,7 +13700,7 @@
         <v>1101</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>1102</v>
@@ -13677,7 +13718,7 @@
         <v>6254</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13691,7 +13732,7 @@
         <v>1106</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>924</v>
@@ -13700,7 +13741,7 @@
         <v>1107</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>1108</v>
@@ -13718,7 +13759,7 @@
         <v>7854</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13732,7 +13773,7 @@
         <v>1112</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>924</v>
@@ -13741,7 +13782,7 @@
         <v>1113</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>1114</v>
@@ -13759,7 +13800,7 @@
         <v>8362</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13773,7 +13814,7 @@
         <v>1118</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>924</v>
@@ -13782,7 +13823,7 @@
         <v>1119</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>1120</v>
@@ -13800,7 +13841,7 @@
         <v>7954</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13814,7 +13855,7 @@
         <v>1124</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>924</v>
@@ -13823,7 +13864,7 @@
         <v>1125</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>1126</v>
@@ -13841,7 +13882,7 @@
         <v>8043</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13855,7 +13896,7 @@
         <v>1130</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>924</v>
@@ -13864,7 +13905,7 @@
         <v>1131</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>1132</v>
@@ -13882,7 +13923,7 @@
         <v>6787</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13896,7 +13937,7 @@
         <v>1136</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>924</v>
@@ -13905,7 +13946,7 @@
         <v>1137</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>1138</v>
@@ -13923,7 +13964,7 @@
         <v>6426</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13937,7 +13978,7 @@
         <v>1142</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>924</v>
@@ -13964,7 +14005,7 @@
         <v>9338</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13978,7 +14019,7 @@
         <v>1149</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>924</v>
@@ -13987,7 +14028,7 @@
         <v>1150</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>1151</v>
@@ -14005,7 +14046,7 @@
         <v>7643</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14019,7 +14060,7 @@
         <v>1155</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>924</v>
@@ -14028,7 +14069,7 @@
         <v>1156</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>1157</v>
@@ -14046,7 +14087,7 @@
         <v>7727</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14060,7 +14101,7 @@
         <v>1161</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>924</v>
@@ -14069,7 +14110,7 @@
         <v>1162</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>1163</v>
@@ -14087,7 +14128,7 @@
         <v>5610</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14101,7 +14142,7 @@
         <v>1167</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>924</v>
@@ -14110,7 +14151,7 @@
         <v>1168</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>1169</v>
@@ -14128,7 +14169,7 @@
         <v>6104</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14142,7 +14183,7 @@
         <v>1173</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>924</v>
@@ -14151,7 +14192,7 @@
         <v>1174</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>1175</v>
@@ -14169,7 +14210,7 @@
         <v>7263</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14183,7 +14224,7 @@
         <v>1179</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>924</v>
@@ -14192,7 +14233,7 @@
         <v>1180</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>1181</v>
@@ -14210,7 +14251,7 @@
         <v>6899</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14224,7 +14265,7 @@
         <v>1185</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>924</v>
@@ -14233,7 +14274,7 @@
         <v>1186</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>1187</v>
@@ -14251,7 +14292,7 @@
         <v>6792</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14265,7 +14306,7 @@
         <v>1191</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>924</v>
@@ -14274,7 +14315,7 @@
         <v>1192</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>1193</v>
@@ -14292,7 +14333,7 @@
         <v>7678</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14306,7 +14347,7 @@
         <v>1197</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>924</v>
@@ -14315,7 +14356,7 @@
         <v>1198</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>1199</v>
@@ -14333,7 +14374,7 @@
         <v>7103</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14347,7 +14388,7 @@
         <v>1203</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>924</v>
@@ -14356,7 +14397,7 @@
         <v>1204</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>1205</v>
@@ -14374,7 +14415,7 @@
         <v>6829</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14388,7 +14429,7 @@
         <v>1209</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>924</v>
@@ -14397,7 +14438,7 @@
         <v>1210</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>1211</v>
@@ -14415,7 +14456,7 @@
         <v>7303</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14429,7 +14470,7 @@
         <v>1215</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>924</v>
@@ -14438,7 +14479,7 @@
         <v>1216</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>1217</v>
@@ -14456,7 +14497,7 @@
         <v>7316</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14470,7 +14511,7 @@
         <v>1221</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>924</v>
@@ -14479,7 +14520,7 @@
         <v>1222</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>1223</v>
@@ -14497,7 +14538,7 @@
         <v>13645</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14511,7 +14552,7 @@
         <v>1227</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>924</v>
@@ -14520,7 +14561,7 @@
         <v>1228</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>1229</v>
@@ -14538,7 +14579,7 @@
         <v>9472</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14552,7 +14593,7 @@
         <v>1233</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>924</v>
@@ -14561,7 +14602,7 @@
         <v>1234</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>1235</v>
@@ -14579,7 +14620,7 @@
         <v>11122</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14593,7 +14634,7 @@
         <v>1239</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>924</v>
@@ -14602,7 +14643,7 @@
         <v>1240</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>1241</v>
@@ -14620,7 +14661,7 @@
         <v>11797</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14634,7 +14675,7 @@
         <v>1245</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>924</v>
@@ -14643,7 +14684,7 @@
         <v>1246</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>1247</v>
@@ -14661,7 +14702,7 @@
         <v>11185</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14675,7 +14716,7 @@
         <v>1251</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>924</v>
@@ -14684,7 +14725,7 @@
         <v>1252</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>1253</v>
@@ -14702,7 +14743,7 @@
         <v>9526</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14716,7 +14757,7 @@
         <v>1257</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>924</v>
@@ -14725,7 +14766,7 @@
         <v>1258</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>1259</v>
@@ -14743,7 +14784,7 @@
         <v>10260</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14757,7 +14798,7 @@
         <v>1263</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>924</v>
@@ -14766,7 +14807,7 @@
         <v>1264</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>1265</v>
@@ -14784,7 +14825,7 @@
         <v>11548</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14798,7 +14839,7 @@
         <v>1269</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>924</v>
@@ -14807,7 +14848,7 @@
         <v>1270</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>1271</v>
@@ -14825,7 +14866,7 @@
         <v>9775</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14839,7 +14880,7 @@
         <v>1275</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>924</v>
@@ -14848,7 +14889,7 @@
         <v>1276</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>1277</v>
@@ -14866,7 +14907,7 @@
         <v>10327</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14880,7 +14921,7 @@
         <v>1281</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>924</v>
@@ -14889,7 +14930,7 @@
         <v>1282</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>1283</v>
@@ -14907,7 +14948,7 @@
         <v>11007</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14921,7 +14962,7 @@
         <v>1287</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>924</v>
@@ -14930,7 +14971,7 @@
         <v>1288</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>1289</v>
@@ -14948,7 +14989,7 @@
         <v>11987</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14962,7 +15003,7 @@
         <v>1293</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>924</v>
@@ -14971,7 +15012,7 @@
         <v>1294</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>1295</v>
@@ -14989,7 +15030,7 @@
         <v>9991</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15003,7 +15044,7 @@
         <v>1299</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>924</v>
@@ -15012,7 +15053,7 @@
         <v>1300</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>1301</v>
@@ -15030,7 +15071,7 @@
         <v>8952</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15044,7 +15085,7 @@
         <v>1305</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>924</v>
@@ -15053,7 +15094,7 @@
         <v>1306</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>1307</v>
@@ -15071,7 +15112,7 @@
         <v>10575</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15085,7 +15126,7 @@
         <v>1311</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>924</v>
@@ -15094,7 +15135,7 @@
         <v>1312</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>1313</v>
@@ -15112,7 +15153,7 @@
         <v>10855</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15126,7 +15167,7 @@
         <v>1317</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>924</v>
@@ -15135,7 +15176,7 @@
         <v>1318</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>1319</v>
@@ -15153,7 +15194,7 @@
         <v>8651</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15167,7 +15208,7 @@
         <v>1323</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>924</v>
@@ -15176,7 +15217,7 @@
         <v>1324</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>1325</v>
@@ -15194,7 +15235,7 @@
         <v>9010</v>
       </c>
       <c r="M71" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15208,7 +15249,7 @@
         <v>1329</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>924</v>
@@ -15217,7 +15258,7 @@
         <v>1330</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>1331</v>
@@ -15235,7 +15276,7 @@
         <v>7961</v>
       </c>
       <c r="M72" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15258,7 +15299,7 @@
         <v>1337</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>1338</v>
@@ -15276,7 +15317,7 @@
         <v>12011</v>
       </c>
       <c r="M73" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15299,7 +15340,7 @@
         <v>1343</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>1344</v>
@@ -15317,7 +15358,7 @@
         <v>8177</v>
       </c>
       <c r="M74" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15358,7 +15399,7 @@
         <v>9158</v>
       </c>
       <c r="M75" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15399,7 +15440,7 @@
         <v>6938</v>
       </c>
       <c r="M76" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15440,7 +15481,7 @@
         <v>7734</v>
       </c>
       <c r="M77" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15481,7 +15522,7 @@
         <v>7602</v>
       </c>
       <c r="M78" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15522,7 +15563,7 @@
         <v>7450</v>
       </c>
       <c r="M79" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15563,7 +15604,7 @@
         <v>6987</v>
       </c>
       <c r="M80" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15604,7 +15645,7 @@
         <v>7114</v>
       </c>
       <c r="M81" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15645,7 +15686,7 @@
         <v>8655</v>
       </c>
       <c r="M82" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15686,7 +15727,7 @@
         <v>8239</v>
       </c>
       <c r="M83" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15727,7 +15768,7 @@
         <v>8021</v>
       </c>
       <c r="M84" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15768,7 +15809,7 @@
         <v>7480</v>
       </c>
       <c r="M85" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15782,7 +15823,7 @@
         <v>1415</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>924</v>
@@ -15791,7 +15832,7 @@
         <v>1416</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H86" s="3" t="s">
         <v>1417</v>
@@ -15809,7 +15850,7 @@
         <v>7087</v>
       </c>
       <c r="M86" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15823,7 +15864,7 @@
         <v>1421</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>924</v>
@@ -15832,7 +15873,7 @@
         <v>1422</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H87" s="3" t="s">
         <v>1423</v>
@@ -15850,7 +15891,7 @@
         <v>6846</v>
       </c>
       <c r="M87" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15864,7 +15905,7 @@
         <v>1427</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>924</v>
@@ -15873,7 +15914,7 @@
         <v>1428</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H88" s="3" t="s">
         <v>1429</v>
@@ -15891,7 +15932,7 @@
         <v>6106</v>
       </c>
       <c r="M88" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15905,7 +15946,7 @@
         <v>1433</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>924</v>
@@ -15914,7 +15955,7 @@
         <v>1434</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>1435</v>
@@ -15932,7 +15973,7 @@
         <v>5490</v>
       </c>
       <c r="M89" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15955,7 +15996,7 @@
         <v>1440</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H90" s="3" t="s">
         <v>1441</v>
@@ -15973,7 +16014,7 @@
         <v>6535</v>
       </c>
       <c r="M90" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15996,7 +16037,7 @@
         <v>1446</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>1447</v>
@@ -16014,7 +16055,7 @@
         <v>6366</v>
       </c>
       <c r="M91" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16037,7 +16078,7 @@
         <v>1452</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H92" s="3" t="s">
         <v>1453</v>
@@ -16055,7 +16096,7 @@
         <v>6623</v>
       </c>
       <c r="M92" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16078,7 +16119,7 @@
         <v>1458</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H93" s="3" t="s">
         <v>1459</v>
@@ -16096,7 +16137,7 @@
         <v>6429</v>
       </c>
       <c r="M93" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16119,7 +16160,7 @@
         <v>1464</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>1465</v>
@@ -16137,7 +16178,7 @@
         <v>6712</v>
       </c>
       <c r="M94" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16151,7 +16192,7 @@
         <v>1469</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>924</v>
@@ -16178,7 +16219,7 @@
         <v>6524</v>
       </c>
       <c r="M95" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16192,7 +16233,7 @@
         <v>1476</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>924</v>
@@ -16201,7 +16242,7 @@
         <v>1477</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>1478</v>
@@ -16219,7 +16260,7 @@
         <v>7611</v>
       </c>
       <c r="M96" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16233,7 +16274,7 @@
         <v>1482</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>924</v>
@@ -16242,7 +16283,7 @@
         <v>1483</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H97" s="3" t="s">
         <v>1484</v>
@@ -16260,7 +16301,7 @@
         <v>7530</v>
       </c>
       <c r="M97" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16274,7 +16315,7 @@
         <v>1488</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>924</v>
@@ -16283,7 +16324,7 @@
         <v>1489</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H98" s="3" t="s">
         <v>1490</v>
@@ -16301,7 +16342,7 @@
         <v>5552</v>
       </c>
       <c r="M98" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16324,7 +16365,7 @@
         <v>1495</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H99" s="3" t="s">
         <v>1496</v>
@@ -16342,7 +16383,7 @@
         <v>5036</v>
       </c>
       <c r="M99" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16356,7 +16397,7 @@
         <v>1500</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>924</v>
@@ -16383,7 +16424,7 @@
         <v>1515</v>
       </c>
       <c r="M100" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16397,7 +16438,7 @@
         <v>1506</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>1507</v>
@@ -16424,7 +16465,7 @@
         <v>2465</v>
       </c>
       <c r="M101" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16438,7 +16479,7 @@
         <v>1513</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>1507</v>
@@ -16465,7 +16506,7 @@
         <v>2135</v>
       </c>
       <c r="M102" s="3" t="s">
-        <v>908</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -16531,7 +16572,7 @@
         <v>1525</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>1526</v>
@@ -17080,7 +17121,7 @@
     </row>
     <row r="33" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>1623</v>
@@ -17538,7 +17579,7 @@
         <v>1707</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1705</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17546,16 +17587,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>1709</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>1710</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>1711</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>1708</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>1709</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>1710</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>1705</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17563,16 +17604,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>1705</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17580,16 +17621,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1703</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>1705</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17597,16 +17638,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1703</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>1705</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17614,16 +17655,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>1705</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17631,16 +17672,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1703</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>1705</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17648,16 +17689,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>1705</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17665,16 +17706,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>1705</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17682,16 +17723,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>1703</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>1705</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17699,16 +17740,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>1703</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>1705</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17716,16 +17757,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>1703</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>1705</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17733,16 +17774,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>1705</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17750,16 +17791,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>1705</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17767,16 +17808,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1703</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>1705</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17784,16 +17825,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>1703</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>1705</v>
+        <v>1708</v>
       </c>
     </row>
   </sheetData>
